--- a/toy-rulebooks/customer-fullname/xlsx/rulebook.xlsx
+++ b/toy-rulebooks/customer-fullname/xlsx/rulebook.xlsx
@@ -1,211 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eejai42/effortlessapi-app-root/users/user_ee42ai73-18a9-47d5-8f99-954b00f6c041/my-projects/effortless-rulebooks/rulebook-examples/customer-fullname/xlsx/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49462916-CC4E-5449-A3ED-B3B8765EEA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" r:id="rId1"/>
-    <sheet name="__meta__" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__meta__" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>ERB Rulebook</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>First Name of the customer</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Last Name of the customer</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>Full name: first and last</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Last letter of first and last name, dot-separated with trailing dot</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>CustomerId</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Initials</t>
-  </si>
-  <si>
-    <t>jane-smith-email-com</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>john-doe-email-com</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>emily-jones-email-com</t>
-  </si>
-  <si>
-    <t>Emily</t>
-  </si>
-  <si>
-    <t>Jones</t>
-  </si>
-  <si>
-    <t>alice-cooper</t>
-  </si>
-  <si>
-    <t>Gutknecht</t>
-  </si>
-  <si>
-    <t>MetaKey</t>
-  </si>
-  <si>
-    <t>ValueType</t>
-  </si>
-  <si>
-    <t>StringValue</t>
-  </si>
-  <si>
-    <t>JsonValue</t>
-  </si>
-  <si>
-    <t>Mary</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,46 +60,126 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>First Name of the customer</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Last Name of the customer</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Full name: first and last</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>First letter of the first and last name</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -544,139 +466,195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CustomerId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FirstName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LastName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Initials</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="str">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>jane-smith</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
         <f>$C2 &amp; ", " &amp; $B2</f>
-        <v>Smith, Jane</v>
-      </c>
-      <c r="E2" s="3" t="str">
-        <f>LEFT($B2, 1) &amp;LEFT($C2, 1) &amp; "-v2"</f>
-        <v>JS-v2</v>
+        <v/>
+      </c>
+      <c r="E2" s="3">
+        <f>LEFT($B2, 1) &amp;LEFT($C2, 1)</f>
+        <v/>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="str">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>john-doe</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Doe</t>
+        </is>
+      </c>
+      <c r="D3" s="3">
         <f>$C3 &amp; ", " &amp; $B3</f>
-        <v>Doe, John</v>
-      </c>
-      <c r="E3" s="3" t="str">
-        <f t="shared" ref="E3:E5" si="0">LEFT($B3, 1) &amp;LEFT($C3, 1) &amp; "-v2"</f>
-        <v>JD-v2</v>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>LEFT($B3, 1) &amp;LEFT($C3, 1)</f>
+        <v/>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3" t="str">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>emily-jones</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
         <f>$C4 &amp; ", " &amp; $B4</f>
-        <v>Jones, Emily</v>
-      </c>
-      <c r="E4" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>EJ-v2</v>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>LEFT($B4, 1) &amp;LEFT($C4, 1)</f>
+        <v/>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3" t="str">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>mary-gutknecht</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Gutknecht</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
         <f>$C5 &amp; ", " &amp; $B5</f>
-        <v>Gutknecht, Mary</v>
-      </c>
-      <c r="E5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>MG-v2</v>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>LEFT($B5, 1) &amp;LEFT($C5, 1)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MetaKey</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ValueType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>StringValue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>JsonValue</t>
+        </is>
       </c>
     </row>
   </sheetData>
